--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="490">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,11 +485,21 @@
     <t>coded-rating</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/pss-coded-rating}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSCodedRating}
 </t>
   </si>
   <si>
     <t>PSS Rating Extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:structured-rating</t>
+  </si>
+  <si>
+    <t>structured-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
+</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -1851,12 +1861,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.28515625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="60.28515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.72265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1864,7 +1874,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="97.3828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="101.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3188,11 +3198,13 @@
         <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3205,26 +3217,22 @@
         <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3272,7 +3280,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3281,7 +3289,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>142</v>
@@ -3293,7 +3301,7 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>82</v>
@@ -3304,14 +3312,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3324,24 +3332,26 @@
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3389,7 +3399,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3401,30 +3411,30 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3432,31 +3442,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3482,13 +3492,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3506,13 +3516,13 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
@@ -3521,27 +3531,27 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3549,7 +3559,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>91</v>
@@ -3558,22 +3568,22 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3599,13 +3609,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3623,10 +3633,10 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>91</v>
@@ -3638,16 +3648,16 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
@@ -3655,10 +3665,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3666,7 +3676,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>91</v>
@@ -3675,22 +3685,22 @@
         <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3701,7 +3711,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3716,13 +3726,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3740,10 +3750,10 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>91</v>
@@ -3755,16 +3765,16 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>82</v>
@@ -3772,10 +3782,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3783,31 +3793,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3818,7 +3828,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -3833,13 +3843,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3857,13 +3867,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3872,16 +3882,16 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3889,10 +3899,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3903,7 +3913,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3912,18 +3922,20 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -3948,13 +3960,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -3972,13 +3984,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3987,16 +3999,16 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4004,10 +4016,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4024,23 +4036,21 @@
         <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4065,13 +4075,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4089,7 +4099,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4104,16 +4114,16 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4121,10 +4131,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4141,21 +4151,23 @@
         <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4204,7 +4216,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4225,7 +4237,7 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
@@ -4236,10 +4248,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4247,7 +4259,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4262,17 +4274,15 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4297,13 +4307,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4321,10 +4331,10 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4336,27 +4346,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>238</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4379,16 +4389,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4414,13 +4424,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4438,7 +4448,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>91</v>
@@ -4453,27 +4463,27 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4481,7 +4491,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
@@ -4493,19 +4503,19 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4555,10 +4565,10 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>91</v>
@@ -4570,27 +4580,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4601,7 +4611,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4613,15 +4623,17 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4670,13 +4682,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -4685,27 +4697,27 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4716,7 +4728,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4725,16 +4737,16 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4785,13 +4797,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -4800,27 +4812,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4843,13 +4855,13 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4900,7 +4912,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4915,27 +4927,27 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4955,16 +4967,16 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5015,7 +5027,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5030,16 +5042,16 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5047,10 +5059,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5070,20 +5082,18 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>182</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5108,13 +5118,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5132,7 +5142,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5147,16 +5157,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5164,10 +5174,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5187,18 +5197,20 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5223,13 +5235,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5247,7 +5259,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5262,16 +5274,16 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5279,10 +5291,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5293,7 +5305,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5305,17 +5317,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5340,13 +5350,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5364,13 +5374,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5379,27 +5389,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5422,16 +5432,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>313</v>
+        <v>185</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5457,13 +5467,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5481,7 +5491,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5496,27 +5506,27 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>178</v>
+        <v>311</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5536,18 +5546,20 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5596,7 +5608,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5611,16 +5623,16 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5628,10 +5640,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5654,13 +5666,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>323</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5711,7 +5723,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5726,13 +5738,13 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -5769,13 +5781,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5841,13 +5853,13 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -5858,10 +5870,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5872,7 +5884,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -5884,18 +5896,16 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>337</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -5943,13 +5953,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -5958,13 +5968,13 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -5975,10 +5985,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5998,21 +6008,21 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6036,13 +6046,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6060,7 +6070,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6075,13 +6085,13 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6092,10 +6102,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6106,7 +6116,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6118,15 +6128,17 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>185</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6151,13 +6163,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6175,13 +6187,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6190,13 +6202,13 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
@@ -6207,10 +6219,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6233,13 +6245,13 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6290,7 +6302,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6305,13 +6317,13 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6322,10 +6334,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6348,17 +6360,15 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6407,7 +6417,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6422,13 +6432,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6439,10 +6449,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6453,7 +6463,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6465,15 +6475,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6522,13 +6534,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6537,13 +6549,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6554,10 +6566,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6580,13 +6592,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6637,7 +6649,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6649,16 +6661,16 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6669,21 +6681,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6695,17 +6707,15 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6754,19 +6764,19 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -6775,7 +6785,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6786,14 +6796,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>384</v>
+        <v>157</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6806,26 +6816,24 @@
         <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6873,7 +6881,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6894,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>134</v>
+        <v>381</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6905,44 +6913,46 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="N44" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -6990,19 +7000,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7011,7 +7021,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>134</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7022,10 +7032,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7048,15 +7058,17 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7105,7 +7117,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7117,7 +7129,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7126,7 +7138,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7137,21 +7149,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7163,17 +7175,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7222,19 +7232,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7243,7 +7253,7 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7254,14 +7264,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>384</v>
+        <v>157</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7274,26 +7284,24 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7341,7 +7349,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7362,7 +7370,7 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>134</v>
+        <v>381</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7373,42 +7381,46 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>397</v>
+        <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7456,19 +7468,19 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7477,7 +7489,7 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>400</v>
+        <v>134</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
@@ -7488,10 +7500,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7514,13 +7526,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7571,7 +7583,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7592,7 +7604,7 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -7603,10 +7615,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7629,13 +7641,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7686,7 +7698,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7707,7 +7719,7 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7744,20 +7756,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>414</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7823,10 +7831,10 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
@@ -7837,10 +7845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7863,18 +7871,20 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -7922,7 +7932,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7940,24 +7950,24 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7980,15 +7990,17 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8037,7 +8049,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8055,24 +8067,24 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8095,17 +8107,15 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8154,7 +8164,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8172,24 +8182,24 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8212,15 +8222,17 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8269,7 +8281,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8287,13 +8299,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8301,10 +8313,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8327,13 +8339,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>368</v>
+        <v>441</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8384,7 +8396,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8402,13 +8414,13 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8416,10 +8428,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8442,13 +8454,13 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>375</v>
+        <v>446</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8499,7 +8511,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8511,16 +8523,16 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -8531,21 +8543,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8557,17 +8569,15 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8616,19 +8626,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -8637,7 +8647,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -8648,14 +8658,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>384</v>
+        <v>157</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8668,26 +8678,24 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -8735,7 +8743,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8756,7 +8764,7 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>134</v>
+        <v>381</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -8767,44 +8775,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>451</v>
+        <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>388</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>389</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -8828,13 +8838,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -8852,42 +8862,42 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>134</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8895,7 +8905,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>91</v>
@@ -8910,15 +8920,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>182</v>
+        <v>454</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -8943,13 +8955,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -8967,10 +8979,10 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>91</v>
@@ -8985,24 +8997,24 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9025,13 +9037,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>468</v>
+        <v>185</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9058,13 +9070,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9082,7 +9094,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9097,38 +9109,38 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9140,17 +9152,15 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9199,13 +9209,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9214,13 +9224,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9231,14 +9241,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9257,16 +9267,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9316,7 +9326,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9331,18 +9341,135 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO64" t="s" s="2">
+      <c r="N65" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="498">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
+    <t>http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-medicationrequest</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -459,10 +462,30 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>MedicationRequest.extension:cpg-rating</t>
-  </si>
-  <si>
-    <t>cpg-rating</t>
+    <t>MedicationRequest.extension:rationale</t>
+  </si>
+  <si>
+    <t>rationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-rationale}
+</t>
+  </si>
+  <si>
+    <t>CPG Rationale Extension</t>
+  </si>
+  <si>
+    <t>A clinician-friendly explanation for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:rating</t>
+  </si>
+  <si>
+    <t>rating</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-rating}
@@ -475,8 +498,10 @@
     <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
+    <t>MedicationRequest.extension:cpg-rating</t>
+  </si>
+  <si>
+    <t>cpg-rating</t>
   </si>
   <si>
     <t>MedicationRequest.extension:coded-rating</t>
@@ -787,7 +812,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-patient)
 </t>
   </si>
   <si>
@@ -820,7 +845,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/uv/cpg/StructureDefinition/cpg-encounter)
 </t>
   </si>
   <si>
@@ -852,10 +877,13 @@
 </t>
   </si>
   <si>
-    <t>Information to support ordering of the medication</t>
-  </si>
-  <si>
-    <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
+    <t>Pertinent information</t>
+  </si>
+  <si>
+    <t>The pertinent positive or negative information relevant to the recommendation.</t>
+  </si>
+  <si>
+    <t>This will typically be the most relevant case features used in determining applicability, but could also be other patient-specific information relevant to interpreting or assessing appropriateness of the recommendation with respect to the patient.</t>
   </si>
   <si>
     <t>Request.supportingInfo</t>
@@ -1038,10 +1066,10 @@
 </t>
   </si>
   <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>A link back to the definition that produced this recommendation. Typically a Plan or Activity Definition.</t>
   </si>
   <si>
     <t>Request.instantiates</t>
@@ -1680,6 +1708,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1861,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.28515625" customWidth="true" bestFit="true"/>
@@ -2031,7 +2074,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2146,7 +2189,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>90</v>
       </c>
@@ -2263,7 +2306,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>98</v>
       </c>
@@ -2378,7 +2421,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2495,7 +2538,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2612,7 +2655,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>119</v>
       </c>
@@ -2729,7 +2772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>127</v>
       </c>
@@ -2846,7 +2889,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>135</v>
       </c>
@@ -2959,7 +3002,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -2980,7 +3023,7 @@
         <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>82</v>
@@ -3076,7 +3119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>149</v>
       </c>
@@ -3097,7 +3140,7 @@
         <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>82</v>
@@ -3112,7 +3155,7 @@
         <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3193,15 +3236,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3211,7 +3254,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3223,13 +3266,13 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3289,7 +3332,7 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>142</v>
@@ -3310,48 +3353,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3399,7 +3440,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3420,7 +3461,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3429,14 +3470,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3457,17 +3500,15 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3516,7 +3557,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3528,41 +3569,41 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3571,21 +3612,23 @@
         <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3609,13 +3652,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3633,42 +3676,42 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3679,10 +3722,10 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -3691,16 +3734,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3726,13 +3769,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3750,13 +3793,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3765,27 +3808,27 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3799,7 +3842,7 @@
         <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>92</v>
@@ -3811,13 +3854,13 @@
         <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3828,7 +3871,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -3843,13 +3886,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3867,7 +3910,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -3882,27 +3925,27 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3913,7 +3956,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3925,16 +3968,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3960,13 +4003,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -3984,13 +4027,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3999,27 +4042,27 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4027,16 +4070,16 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>92</v>
@@ -4045,12 +4088,14 @@
         <v>111</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4060,7 +4105,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -4075,13 +4120,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4099,10 +4144,10 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -4114,27 +4159,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4145,28 +4190,28 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4192,13 +4237,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4216,13 +4261,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4234,24 +4279,24 @@
         <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4265,7 +4310,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>82</v>
@@ -4274,13 +4319,13 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4307,13 +4352,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4331,7 +4376,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4346,27 +4391,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4374,31 +4419,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4424,13 +4469,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4448,10 +4493,10 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>91</v>
@@ -4463,27 +4508,27 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>238</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4491,7 +4536,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
@@ -4506,17 +4551,15 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4565,10 +4608,10 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>91</v>
@@ -4580,27 +4623,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4608,31 +4651,31 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4658,13 +4701,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4682,10 +4725,10 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>91</v>
@@ -4697,27 +4740,27 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4725,30 +4768,32 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4797,13 +4842,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -4812,27 +4857,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AO25" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4846,24 +4891,26 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4912,7 +4959,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4927,27 +4974,27 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>273</v>
+        <v>188</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4958,27 +5005,29 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5027,13 +5076,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5042,27 +5091,27 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5082,16 +5131,16 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5142,7 +5191,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5157,27 +5206,27 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5200,17 +5249,15 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5235,13 +5282,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5259,7 +5306,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5274,27 +5321,27 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5317,13 +5364,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5374,7 +5421,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5389,27 +5436,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5420,7 +5467,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5429,19 +5476,19 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5467,13 +5514,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5491,13 +5538,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5506,27 +5553,27 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5537,7 +5584,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5549,17 +5596,15 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5608,13 +5653,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5623,27 +5668,27 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5663,18 +5708,20 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>323</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5699,13 +5746,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5723,7 +5770,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5738,27 +5785,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5778,18 +5825,20 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5838,7 +5887,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5853,27 +5902,27 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5887,7 +5936,7 @@
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -5896,13 +5945,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5953,7 +6002,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5968,27 +6017,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5999,7 +6048,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6011,18 +6060,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6070,13 +6117,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6085,13 +6132,13 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6100,12 +6147,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6116,7 +6163,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6125,20 +6172,18 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>340</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6163,13 +6208,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6187,13 +6232,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6202,13 +6247,13 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
@@ -6217,12 +6262,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6233,7 +6278,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6242,19 +6287,21 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>351</v>
+        <v>171</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6302,13 +6349,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6317,13 +6364,13 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6332,12 +6379,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6348,7 +6395,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6360,15 +6407,17 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>357</v>
+        <v>192</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6393,13 +6442,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6417,13 +6466,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6432,13 +6481,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6447,12 +6496,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6475,17 +6524,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6534,7 +6581,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6549,13 +6596,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6564,12 +6611,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6580,7 +6627,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6592,13 +6639,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6649,13 +6696,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -6664,13 +6711,13 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6679,12 +6726,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6695,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6707,15 +6754,17 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6764,28 +6813,28 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6794,23 +6843,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6822,17 +6871,15 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6881,28 +6928,28 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6911,48 +6958,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>385</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7000,53 +7043,53 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7058,16 +7101,16 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>371</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>394</v>
+        <v>167</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7117,19 +7160,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7138,7 +7181,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7147,44 +7190,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>377</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7232,19 +7279,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7253,7 +7300,7 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>381</v>
+        <v>134</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7262,23 +7309,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7290,16 +7337,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>160</v>
+        <v>402</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7349,19 +7396,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7370,7 +7417,7 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7379,48 +7426,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>136</v>
+        <v>385</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7468,19 +7511,19 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7489,7 +7532,7 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>134</v>
+        <v>389</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
@@ -7498,23 +7541,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7526,15 +7569,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>400</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7583,19 +7628,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7604,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -7613,44 +7658,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7698,19 +7747,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7719,7 +7768,7 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>134</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7728,12 +7777,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7756,13 +7805,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7813,7 +7862,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7834,7 +7883,7 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
@@ -7843,7 +7892,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>412</v>
       </c>
@@ -7879,12 +7928,8 @@
       <c r="M52" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -7950,10 +7995,10 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
@@ -7962,12 +8007,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7990,17 +8035,15 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8049,7 +8092,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8067,24 +8110,24 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8107,16 +8150,20 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8164,7 +8211,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8182,24 +8229,24 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8222,16 +8269,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8281,7 +8328,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8299,24 +8346,24 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8339,13 +8386,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8396,7 +8443,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8414,24 +8461,24 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8454,15 +8501,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8511,7 +8560,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8529,24 +8578,24 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8569,13 +8618,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>378</v>
+        <v>450</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>379</v>
+        <v>451</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8626,7 +8675,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8638,7 +8687,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -8647,32 +8696,32 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8684,17 +8733,15 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>383</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -8743,28 +8790,28 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>385</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>381</v>
+        <v>457</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -8773,48 +8820,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>385</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -8862,19 +8905,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -8883,7 +8926,7 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>134</v>
+        <v>389</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -8892,23 +8935,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -8920,16 +8963,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>454</v>
+        <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>455</v>
+        <v>391</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>456</v>
+        <v>392</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>457</v>
+        <v>167</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8955,13 +8998,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -8979,74 +9022,78 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="B62" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>396</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9070,13 +9117,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9094,42 +9141,42 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>462</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>468</v>
+        <v>134</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9137,7 +9184,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>91</v>
@@ -9152,15 +9199,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9185,13 +9234,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9209,10 +9258,10 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>91</v>
@@ -9224,38 +9273,38 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9267,17 +9316,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>478</v>
+        <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9302,13 +9349,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9326,13 +9373,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9344,24 +9391,24 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9372,7 +9419,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9384,17 +9431,15 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9443,13 +9488,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -9458,22 +9503,274 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM65" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO65" t="s" s="2">
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO67">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI66">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2389" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -496,35 +496,6 @@
   </si>
   <si>
     <t>A clinician-friendly rating, or score, for the recommendation; patient-friendly if the recommendation is patient-facing.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:cpg-rating</t>
-  </si>
-  <si>
-    <t>cpg-rating</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:coded-rating</t>
-  </si>
-  <si>
-    <t>coded-rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSCodedRating}
-</t>
-  </si>
-  <si>
-    <t>PSS Rating Extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:structured-rating</t>
-  </si>
-  <si>
-    <t>structured-rating</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSStructuredRating}
-</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -1904,12 +1875,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO67"/>
+  <dimension ref="A1:AO64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.28515625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="60.28515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1917,7 +1888,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="101.08984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.99609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3241,41 +3212,43 @@
         <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3323,7 +3296,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3344,7 +3317,7 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>82</v>
@@ -3355,14 +3328,12 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3371,10 +3342,10 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>82</v>
@@ -3383,15 +3354,17 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3440,7 +3413,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3452,63 +3425,63 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3533,13 +3506,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3557,31 +3530,31 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3589,46 +3562,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3652,13 +3623,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>82</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3676,28 +3647,28 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -3708,10 +3679,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3719,31 +3690,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3754,7 +3725,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3769,13 +3740,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3793,13 +3764,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3808,27 +3779,27 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3836,31 +3807,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3886,13 +3857,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3910,13 +3881,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3925,16 +3896,16 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3942,10 +3913,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3959,26 +3930,24 @@
         <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4003,13 +3972,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -4027,7 +3996,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4042,16 +4011,16 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4059,10 +4028,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4070,7 +4039,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4085,16 +4054,16 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4105,7 +4074,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -4120,13 +4089,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4144,10 +4113,10 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -4159,16 +4128,16 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4176,10 +4145,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4190,29 +4159,27 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4237,13 +4204,13 @@
         <v>82</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>82</v>
@@ -4261,13 +4228,13 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
@@ -4279,13 +4246,13 @@
         <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4293,10 +4260,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4304,7 +4271,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4319,15 +4286,17 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4352,13 +4321,13 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4376,10 +4345,10 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4391,27 +4360,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4419,7 +4388,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>91</v>
@@ -4428,22 +4397,22 @@
         <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4493,10 +4462,10 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>91</v>
@@ -4508,27 +4477,27 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4542,24 +4511,26 @@
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4608,7 +4579,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4623,27 +4594,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4651,10 +4622,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>92</v>
@@ -4663,19 +4634,19 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4701,13 +4672,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>243</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4725,13 +4696,13 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
@@ -4740,27 +4711,27 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4768,13 +4739,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4783,17 +4754,15 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4842,10 +4811,10 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>91</v>
@@ -4857,27 +4826,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4891,26 +4860,24 @@
         <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4959,7 +4926,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4974,27 +4941,27 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5005,10 +4972,10 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
@@ -5017,17 +4984,15 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5076,13 +5041,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5091,16 +5056,16 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5108,10 +5073,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5134,15 +5099,17 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>277</v>
+        <v>183</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5167,13 +5134,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5191,7 +5158,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5206,27 +5173,27 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5246,16 +5213,16 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5306,7 +5273,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5321,16 +5288,16 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5338,10 +5305,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5352,7 +5319,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5364,15 +5331,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5397,13 +5366,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5421,13 +5390,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5436,27 +5405,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5467,7 +5436,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5476,19 +5445,19 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5514,13 +5483,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5538,13 +5507,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5553,16 +5522,16 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5570,10 +5539,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5584,25 +5553,25 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5653,13 +5622,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -5668,16 +5637,16 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5685,10 +5654,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5708,20 +5677,18 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5746,13 +5713,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5770,7 +5737,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5785,27 +5752,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5825,20 +5792,18 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5887,7 +5852,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5902,16 +5867,16 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5919,10 +5884,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5933,10 +5898,10 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -5945,16 +5910,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6002,13 +5969,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6017,13 +5984,13 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
@@ -6034,10 +6001,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6048,7 +6015,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6057,18 +6024,20 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6093,13 +6062,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6117,13 +6086,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6138,7 +6107,7 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
@@ -6149,10 +6118,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6172,16 +6141,16 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6232,7 +6201,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6247,13 +6216,13 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
@@ -6264,10 +6233,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6278,7 +6247,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6287,21 +6256,19 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>171</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>348</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6349,13 +6316,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6364,13 +6331,13 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
@@ -6381,10 +6348,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6395,7 +6362,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6407,16 +6374,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>192</v>
+        <v>363</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6442,13 +6409,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6466,13 +6433,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6481,13 +6448,13 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>82</v>
@@ -6498,10 +6465,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6512,7 +6479,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6524,13 +6491,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6581,13 +6548,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6596,13 +6563,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -6613,10 +6580,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6627,7 +6594,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6639,13 +6606,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6696,28 +6663,28 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>368</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -6728,14 +6695,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6754,16 +6721,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>375</v>
+        <v>158</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6813,7 +6780,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6825,16 +6792,16 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -6845,42 +6812,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6928,28 +6899,28 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>134</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
@@ -6960,10 +6931,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6986,15 +6957,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7043,7 +7016,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7055,7 +7028,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7064,7 +7037,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7075,21 +7048,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7101,17 +7074,15 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>376</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7160,19 +7131,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7181,7 +7152,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7192,14 +7163,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>395</v>
+        <v>155</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7212,26 +7183,24 @@
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7279,7 +7248,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7300,7 +7269,7 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7311,44 +7280,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7396,19 +7367,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7417,7 +7388,7 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>403</v>
+        <v>134</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7428,10 +7399,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7454,13 +7425,13 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7511,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7523,7 +7494,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7532,7 +7503,7 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
@@ -7543,21 +7514,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7569,17 +7540,15 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7628,19 +7597,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7649,7 +7618,7 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -7660,46 +7629,42 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7747,19 +7712,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7768,7 +7733,7 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>134</v>
+        <v>407</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7779,10 +7744,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7805,16 +7770,20 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7862,7 +7831,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7880,10 +7849,10 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>
@@ -7894,10 +7863,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7920,15 +7889,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -7977,7 +7948,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7995,24 +7966,24 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8035,13 +8006,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8092,7 +8063,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8110,24 +8081,24 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8150,20 +8121,18 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8211,7 +8180,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8229,10 +8198,10 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8243,10 +8212,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8269,17 +8238,15 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8328,7 +8295,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8346,24 +8313,24 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8386,13 +8353,13 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>408</v>
+        <v>370</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8443,7 +8410,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8461,24 +8428,24 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8501,17 +8468,15 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>413</v>
+        <v>376</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>443</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8560,7 +8525,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>379</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8572,16 +8537,16 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>447</v>
+        <v>380</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -8592,21 +8557,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8618,15 +8583,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>449</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8675,19 +8642,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>448</v>
+        <v>384</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -8696,10 +8663,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>452</v>
+        <v>380</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -8707,42 +8674,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>454</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -8790,28 +8761,28 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>453</v>
+        <v>389</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>457</v>
+        <v>134</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -8822,10 +8793,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8833,7 +8804,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>91</v>
@@ -8848,15 +8819,17 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>385</v>
+        <v>453</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>386</v>
+        <v>454</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -8881,13 +8854,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -8905,10 +8878,10 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>91</v>
@@ -8917,41 +8890,41 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>389</v>
+        <v>459</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -8963,17 +8936,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -8998,13 +8969,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9022,78 +8993,74 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>389</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>136</v>
+        <v>470</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>396</v>
+        <v>471</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9141,28 +9108,28 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>134</v>
+        <v>474</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9173,21 +9140,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9199,16 +9166,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9234,13 +9201,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9258,13 +9225,13 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
@@ -9276,24 +9243,24 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>469</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9304,7 +9271,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9316,15 +9283,17 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>483</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9349,13 +9318,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9373,13 +9342,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9388,372 +9357,23 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO67">
+  <autoFilter ref="A1:AO64">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9763,7 +9383,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI66">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSResponseMedicationRequest</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSResponseMedicationRequest</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSResponseMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
